--- a/Microsoft_Certification_Projects/NCAA_Tshirt_vendor.xlsx
+++ b/Microsoft_Certification_Projects/NCAA_Tshirt_vendor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\NCAA_Tshirt_vendor_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Microsoft_Certification_Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4F42AB-3109-4045-B14A-D9903B13CB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E099E68E-C4C0-45F2-A66B-24D0026E9373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38487FD0-083B-4E28-99A7-33AC254CCE98}"/>
   </bookViews>
@@ -142,12 +142,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -156,7 +171,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -168,6 +183,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="60% - Accent3" xfId="2" builtinId="40"/>
@@ -745,7 +761,7 @@
         <f>MIN(B15,B16)</f>
         <v>1450</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C17" s="7" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B17)</f>
         <v>=MIN(B15,B16)</v>
       </c>
@@ -758,7 +774,7 @@
         <f>MAX(B16-B15, 0)</f>
         <v>50</v>
       </c>
-      <c r="C18" t="str">
+      <c r="C18" s="7" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B18)</f>
         <v>=MAX(B16-B15, 0)</v>
       </c>

--- a/Microsoft_Certification_Projects/NCAA_Tshirt_vendor.xlsx
+++ b/Microsoft_Certification_Projects/NCAA_Tshirt_vendor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Microsoft_Certification_Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E099E68E-C4C0-45F2-A66B-24D0026E9373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD6A6DE-A6B7-44E3-90D1-BD9FC10B8200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38487FD0-083B-4E28-99A7-33AC254CCE98}"/>
   </bookViews>
